--- a/02_加值成品/九下/九下2-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下2-4_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下2-4 電磁感應　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三下學期 九下2-4 電磁感應　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>磁場變化使線圈產生電流稱？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>為零</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>電磁感應</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>磁生電</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>電磁感應由誰發現？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>法拉第</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>感應電流</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>電磁感應</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>為零</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>發現</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>產生感應電流需要磁場？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>發生變化</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>電磁感應</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>法拉第</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>變化</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>發電機把動能轉成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>電能</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>感應電流</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>動能轉電能</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>法拉第</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>發電</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>磁鐵與線圈相對運動會產生？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>磁場越強越大</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>感應電流</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>法拉第</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>感應</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>運動越快感應電流？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>發生變化</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>為零</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>電磁感應</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>速度</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>線圈匝數越多感應電流？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>法拉第</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>磁場越強越大</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>匝數</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>磁鐵靜止放線圈中有感應電流嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>沒有</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>為零</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>法拉第</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>無變化</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>發電機是把動能轉成什麼能？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>電能</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>法拉第</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>發電</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>磁場變化使線圈產生的電流稱？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>磁場越強越大</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>感應電流</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>感應</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下2-4 電磁感應　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三下學期 九下2-4 電磁感應　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>感應電流大小與磁場強弱？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>磁場越強越大</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>法拉第</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>磁場</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>發電機與馬達原理關係？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>發生變化</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>動能轉電能</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>相反</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>互逆</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>電磁感應與磁效應方向？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>加快運動增匝數增磁場</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>一是磁生電一是電生磁</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>加快轉速增加匝數用更強磁鐵</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>相反(磁生電vs電生磁)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>抽出磁鐵也能產生感應電流嗎？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>能</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>法拉第</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>動能轉電能</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>有變化</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>要增大感應電流可？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>搖動使線圈磁場變化生電</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>磁通量變化方向不同</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>需磁場變化才有電磁感應</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>加快運動增匝數增磁場</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>增大</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>發電機能量轉換是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>動能轉電能</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>感應電流</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>電磁感應</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>磁通量不變時感應電流？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>電磁感應</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>為零</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>無變化</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>手搖發電是把什麼能轉電？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>馬達電→動、發電機動→電</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>相反(磁生電vs電生磁)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>動能(力學能)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>加快運動增匝數增磁場</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>磁鐵抽出線圈也能產生感應電流嗎？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>發生變化</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>能</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>有變化</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>線圈匝數越多感應電流？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>電磁感應</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>磁場越強越大</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>匝數</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下2-4 電磁感應　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三下學期 九下2-4 電磁感應　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何磁鐵必須運動才產生感應電流？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>一是磁生電一是電生磁</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>需磁場變化才有電磁感應</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>相反(磁生電vs電生磁)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>磁通量變化方向不同</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>變化</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>比較馬達與發電機的能量轉換？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>動能(力學能)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>磁通量變化方向不同</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>需磁場變化才有電磁感應</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>馬達電→動、發電機動→電</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>互逆</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>如何增大發電機的感應電流？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>動能(力學能)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>水力火力核能等帶動轉動</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>一是磁生電一是電生磁</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>加快轉速增加匝數用更強磁鐵</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>增大</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>感應爐加熱鍋具的原理？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>水力火力核能等</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>需磁場變化才有電磁感應</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>動能(力學能)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>變化磁場在鍋底感應電流生熱</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>電磁感應與電流磁效應如何互為表裡？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>一是磁生電一是電生磁</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>需磁場變化才有電磁感應</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>相反(磁生電vs電生磁)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>加快運動增匝數增磁場</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>關聯</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>手搖發電手電筒無電池仍發光原因？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>搖動使線圈磁場變化生電</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>水力火力核能等</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>加快運動增匝數增磁場</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>需磁場變化才有電磁感應</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>磁鐵進出線圈電流方向為何相反？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>加快轉速增加匝數用更強磁鐵</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>馬達電→動、發電機動→電</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>磁通量變化方向不同</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>加快運動增匝數增磁場</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>大型發電廠多用什麼帶動發電機？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>相反(磁生電vs電生磁)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>搖動使線圈磁場變化生電</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>需磁場變化才有電磁感應</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>水力火力核能等帶動轉動</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>發電</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何磁鐵必須運動才有感應電流？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>加快轉速增加匝數用更強磁鐵</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>需磁場變化才有電磁感應</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>動能(力學能)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>水力火力核能等</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>變化</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>大型發電廠用什麼帶動發電機？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>馬達電→動、發電機動→電</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>水力火力核能等</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>水力火力核能等帶動轉動</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>加快轉速增加匝數用更強磁鐵</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>發電</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九下/九下2-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下2-4_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>磁生電</t>
+          <t>磁生電：當穿過線圈的磁場發生變化時，線圈會自己產生電流，這現象叫電磁感應</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>發現</t>
+          <t>發現：科學家法拉第最早發現磁場變化能使線圈產生感應電流，這就是電磁感應的由來</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>變化</t>
+          <t>變化：一定要讓穿過線圈的磁場發生改變，線圈裡才會產生感應電流</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>發電</t>
+          <t>發電：發電機的作用是利用電磁感應，把轉動的動能轉換成電能輸出</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>感應</t>
+          <t>感應：讓磁鐵和線圈之間有相對的移動，會使線圈感受到磁場變化而產生感應電流</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>速度</t>
+          <t>速度：磁鐵和線圈相對移動的速度越快，磁場變化得越快，感應電流也越大</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>匝數</t>
+          <t>匝數：線圈繞的圈數越多，累積產生的感應電流就會越大</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>無變化</t>
+          <t>無變化：磁鐵如果靜止不動，穿過線圈的磁場沒有改變，就不會產生感應電流</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>發電</t>
+          <t>發電：發電機利用電磁感應，把輸入的動能轉換成電能輸出</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>感應</t>
+          <t>感應：穿過線圈的磁場發生變化時，線圈裡自動產生的電流稱為感應電流</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>磁場</t>
+          <t>磁場：使用磁性越強的磁鐵，磁場變化的程度越大，感應電流也就越大</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>互逆</t>
+          <t>互逆：發電機是把動能轉成電能，馬達則是把電能轉成動能，兩者原理正好相反</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：電磁感應是磁場變化產生電流(磁生電)，電流的磁效應則是電流產生磁場(電生磁)，方向相反</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>有變化</t>
+          <t>有變化：把磁鐵從線圈中抽出時，穿過線圈的磁場同樣在改變，所以也會產生感應電流</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>磁通量變化方向不同</t>
+          <t>磁場變化方向不同</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>增大</t>
+          <t>增大：加快磁鐵與線圈的相對運動速度、增加線圈的匝數，或使用更強的磁鐵，都能讓感應電流變大</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：發電機運轉時，是利用電磁感應把輸入的動能轉換成電能輸出</t>
         </is>
       </c>
     </row>
@@ -1274,37 +1274,37 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>磁通量不變時感應電流？</t>
+          <t>磁場不變時感應電流？</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>感應電流</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>電磁感應</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>為零</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>能</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>相反</t>
-        </is>
-      </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>無變化</t>
+          <t>無變化：如果穿過線圈的磁場保持固定沒有變化，線圈裡就不會產生感應電流</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：手搖發電筒是靠手部搖動提供動能，透過電磁感應轉換成電能來發光</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>有變化</t>
+          <t>有變化：把磁鐵從線圈中抽出時，穿過線圈的磁場同樣在改變，所以也會產生感應電流</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>匝數</t>
+          <t>匝數：線圈繞的圈數越多，累積產生的感應電流也會越大</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>磁通量變化方向不同</t>
+          <t>磁場變化方向不同</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>變化</t>
+          <t>變化：電磁感應必須要有磁場的變化才會發生，磁鐵靜止不動時磁場沒有改變，自然不會產生感應電流</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>磁通量變化方向不同</t>
+          <t>磁場變化方向不同</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>互逆</t>
+          <t>互逆：馬達是輸入電能、輸出動能，讓裝置轉動；發電機則相反，是輸入動能、輸出電能，兩者互為逆過程</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>增大</t>
+          <t>增大：讓發電機轉得更快、線圈繞更多圈，或換用磁性更強的磁鐵，都能讓輸出的感應電流變大</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：感應爐產生快速變化的磁場，使鍋底金屬中感應出電流，電流通過金屬的電阻產生熱來加熱食物</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>關聯</t>
+          <t>關聯：電流的磁效應是電流產生磁場，電磁感應則是磁場變化產生電流，兩者方向相反卻互相呼應，說明電與磁密不可分</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：搖動手電筒時內部磁鐵與線圈產生相對運動，磁場跟著變化而感應出電流，讓燈泡發光，不需要電池</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>磁通量變化方向不同</t>
+          <t>磁場變化方向不同</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>方向</t>
+          <t>方向：磁鐵靠近線圈和離開線圈時，線圈內磁場增強或減弱的變化方向剛好相反，所以感應出的電流方向也會相反</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>發電</t>
+          <t>發電：大型發電廠常利用水力、火力燃燒或核能產生的高溫蒸氣等方式，帶動發電機裡的線圈或磁鐵轉動來發電</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>變化</t>
+          <t>變化：電磁感應一定要有磁場的變化才會發生，磁鐵靜止不動時磁場沒有改變，就不會產生感應電流</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>發電</t>
+          <t>發電：大型發電廠常利用水力衝擊、燃燒產生的高溫蒸氣等方式，帶動發電機轉動來發電</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九下/九下2-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下2-4_三種難度測驗卷.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>動能轉電能</t>
+          <t>沒有</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
+          <t>法拉第</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
           <t>發生變化</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>為零</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>電磁感應</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>電能</t>
+          <t>相反</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>法拉第</t>
+          <t>發生變化</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>磁場越強越大</t>
+          <t>電磁感應</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>發生變化</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>感應電流</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>法拉第</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>沒有</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>越大</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1044,17 +1044,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>沒有</t>
+          <t>電磁感應</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>電能</t>
+          <t>法拉第</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>法拉第</t>
+          <t>動能轉電能</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>法拉第</t>
+          <t>感應電流</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>為零</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>動能轉電能</t>
+          <t>越大</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1244,17 +1244,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>感應電流</t>
+          <t>發生變化</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>電磁感應</t>
+          <t>越大</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>能</t>
+          <t>磁場越強越大</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>電能</t>
+          <t>沒有</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>發生變化</t>
+          <t>感應電流</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>越大</t>
+          <t>為零</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>電磁感應</t>
+          <t>法拉第</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>磁場越強越大</t>
+          <t>相反</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>能</t>
+          <t>為零</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>相反(磁生電vs電生磁)</t>
+          <t>磁場變化方向不同</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>需磁場變化才有電磁感應</t>
+          <t>加快運動增匝數增磁場</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>馬達電→動、發電機動→電</t>
+          <t>加快運動增匝數增磁場</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>水力火力核能等帶動轉動</t>
+          <t>需磁場變化才有電磁感應</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
